--- a/Calling.xlsx
+++ b/Calling.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\CallingMachine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\CallingMachine\CallingMachine\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -383,7 +383,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1">
+        <v>91911882</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="2"/>
